--- a/Lista_Variaveis.xlsx
+++ b/Lista_Variaveis.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paulo\Documents\Repositorios\Macroeconomic_Variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D2E247-B812-4232-AA27-B0B2F6064DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21DF9BC-0A49-4E9B-A608-0026A224627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D192888-8FF8-4A4B-8588-E6DD82BA1E80}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Var. Samba - Versão Tradicional" sheetId="1" r:id="rId1"/>
+    <sheet name="Var. Samba - Versão Recente" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Var. Samba - Versão Tradicional'!$C$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
     <author>tc={F08322B0-F2AD-4288-8124-9C40D052E509}</author>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{DD306678-CB13-40DC-BEB4-2A13CD863134}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{DD306678-CB13-40DC-BEB4-2A13CD863134}">
       <text>
         <t xml:space="preserve">[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -56,7 +57,7 @@
     consumo final da administração pública </t>
       </text>
     </comment>
-    <comment ref="B18" authorId="1" shapeId="0" xr:uid="{F08322B0-F2AD-4288-8124-9C40D052E509}">
+    <comment ref="C19" authorId="1" shapeId="0" xr:uid="{F08322B0-F2AD-4288-8124-9C40D052E509}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="85">
   <si>
     <t>Série</t>
   </si>
@@ -249,13 +250,88 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Inflação (IPCA)</t>
+  </si>
+  <si>
+    <t>Inflação (IPCA - Preços Adm.)</t>
+  </si>
+  <si>
+    <t>Inflação (IPCA - Preços Livres)</t>
+  </si>
+  <si>
+    <t>Inflação de Expectativas</t>
+  </si>
+  <si>
+    <t>Hiato PIB</t>
+  </si>
+  <si>
+    <t>Cresc. Cons. Governo</t>
+  </si>
+  <si>
+    <t>Cresc. Investimento</t>
+  </si>
+  <si>
+    <t>Cresc. Consumo</t>
+  </si>
+  <si>
+    <t>Cresc. PIB</t>
+  </si>
+  <si>
+    <t>Cresc. Importações</t>
+  </si>
+  <si>
+    <t>Cresc. Exportações</t>
+  </si>
+  <si>
+    <t>Preço Exportações</t>
+  </si>
+  <si>
+    <t>Inflação do Preços das Importações</t>
+  </si>
+  <si>
+    <t>Taxa de Desemprego</t>
+  </si>
+  <si>
+    <t>Taxa de Participação</t>
+  </si>
+  <si>
+    <t>Crescimento do Salário Nominal</t>
+  </si>
+  <si>
+    <t>Taxa de Câmbio Real</t>
+  </si>
+  <si>
+    <t>Taxa de Juros</t>
+  </si>
+  <si>
+    <t>Prêmio de Risco</t>
+  </si>
+  <si>
+    <t>Resultado Primário - Meta</t>
+  </si>
+  <si>
+    <t>Resultado Primário</t>
+  </si>
+  <si>
+    <t>Dados Originais</t>
+  </si>
+  <si>
+    <t>Dados Transformados</t>
+  </si>
+  <si>
+    <t>Poderia ser obtida calculando a taxa acumulada para o trimestre</t>
+  </si>
+  <si>
+    <t>Taxa acumulada do trimestre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,16 +359,22 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="6"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="6"/>
-      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -316,7 +398,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -324,16 +406,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -344,18 +502,105 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,10 +942,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B7" dT="2026-07-02T16:42:37.47" personId="{25B3932A-7D5F-4FEB-8038-9DB41ED8A63D}" id="{DD306678-CB13-40DC-BEB4-2A13CD863134}">
+  <threadedComment ref="C8" dT="2026-07-02T16:42:37.47" personId="{25B3932A-7D5F-4FEB-8038-9DB41ED8A63D}" id="{DD306678-CB13-40DC-BEB4-2A13CD863134}">
     <text xml:space="preserve">consumo final da administração pública </text>
   </threadedComment>
-  <threadedComment ref="B18" dT="2026-07-04T12:15:37.87" personId="{25B3932A-7D5F-4FEB-8038-9DB41ED8A63D}" id="{F08322B0-F2AD-4288-8124-9C40D052E509}">
+  <threadedComment ref="C19" dT="2026-07-04T12:15:37.87" personId="{25B3932A-7D5F-4FEB-8038-9DB41ED8A63D}" id="{F08322B0-F2AD-4288-8124-9C40D052E509}">
     <text>Somente Indústria de Transformação</text>
   </threadedComment>
 </ThreadedComments>
@@ -708,623 +953,1703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E1C810-AA64-4EE6-A2D9-D85B15ADACA6}">
-  <dimension ref="B1:J23"/>
+  <dimension ref="B1:S47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="20.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="20.7109375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="1.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="34" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="15" customWidth="1"/>
+    <col min="12" max="12" width="33.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" style="15" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" style="15" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" style="15" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="15"/>
+    <col min="17" max="17" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B2" s="11"/>
+      <c r="C2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
+      <c r="L2" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="14"/>
+    </row>
+    <row r="3" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G3" s="18">
         <v>2072</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="H3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="19" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="L3" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="21">
+        <v>1737</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="23">
+        <v>2</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G4" s="21">
         <v>1737</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="H4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="L4" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="21">
+        <v>4449</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="23">
+        <v>3</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F5" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G5" s="21">
         <v>6470</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="H5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+      <c r="L5" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="21">
+        <v>11428</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="S5" s="22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="23">
+        <v>4</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="11" t="s">
+      <c r="H6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
+      <c r="L6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="22"/>
+    </row>
+    <row r="7" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="23">
+        <v>5</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
+      <c r="L7" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="22"/>
+    </row>
+    <row r="8" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="23">
+        <v>6</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G8" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="H8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
+      <c r="L8" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="22"/>
+    </row>
+    <row r="9" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="23">
+        <v>7</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D9" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F9" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H9" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="I9" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+      <c r="L9" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="22"/>
+    </row>
+    <row r="10" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="23">
+        <v>8</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G10" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="I10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+      <c r="L10" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="22"/>
+    </row>
+    <row r="11" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="23">
+        <v>9</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D11" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="11" t="s">
+      <c r="I11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
+      <c r="L11" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="22"/>
+    </row>
+    <row r="12" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="23">
+        <v>10</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G12" s="21">
         <v>28763</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="11" t="s">
+      <c r="H12" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
+      <c r="L12" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="22"/>
+    </row>
+    <row r="13" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="23">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C13" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F13" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="G13" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="I13" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J13" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
+      <c r="L13" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="22"/>
+    </row>
+    <row r="14" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="23">
+        <v>12</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D14" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="E14" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="F14" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G14" s="21">
         <v>13521</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H14" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="11" t="s">
+      <c r="I14" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="5" t="s">
+      <c r="L14" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="22"/>
+    </row>
+    <row r="15" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="23">
+        <v>13</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E15" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F15" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G15" s="21">
         <v>4449</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H15" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="I15" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
+      <c r="L15" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="22"/>
+    </row>
+    <row r="16" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="23">
+        <v>14</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E16" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="F16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G16" s="21">
         <v>11428</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="H16" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="11" t="s">
+      <c r="I16" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="5" t="s">
+      <c r="L16" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="22"/>
+    </row>
+    <row r="17" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="23">
+        <v>15</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D17" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="E17" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F17" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G17" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="H17" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="11" t="s">
+      <c r="I17" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
+      <c r="L17" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="22"/>
+    </row>
+    <row r="18" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="23">
+        <v>16</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D18" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E18" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F18" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G18" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H18" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" s="11" t="s">
+      <c r="I18" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
+      <c r="L18" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="22"/>
+    </row>
+    <row r="19" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="23">
+        <v>17</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D19" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E19" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F19" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="9">
+      <c r="G19" s="27">
         <v>28561</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H19" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="J18" s="11" t="s">
+      <c r="I19" s="27"/>
+      <c r="J19" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
+      <c r="L19" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="22"/>
+    </row>
+    <row r="20" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="23">
+        <v>18</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D20" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="E20" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F20" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G20" s="21">
         <v>4649</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H20" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19" s="10" t="s">
+      <c r="I20" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="28" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
+      <c r="L20" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="22"/>
+    </row>
+    <row r="21" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="23">
+        <v>19</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D21" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E21" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F21" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G21" s="21">
         <v>5784</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="H21" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" s="10" t="s">
+      <c r="I21" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="28" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="5" t="s">
+      <c r="L21" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="22"/>
+    </row>
+    <row r="22" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="23">
+        <v>20</v>
+      </c>
+      <c r="C22" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D22" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="E22" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F22" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G22" s="21">
         <v>28763</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H22" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="11" t="s">
+      <c r="I22" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="5" t="s">
+      <c r="L22" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="22"/>
+    </row>
+    <row r="23" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="23">
+        <v>21</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D23" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="E23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="F23" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G23" s="21">
         <v>1344</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="11" t="s">
+      <c r="H23" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+      <c r="L23" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="31"/>
+    </row>
+    <row r="24" spans="2:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="32">
+        <v>22</v>
+      </c>
+      <c r="C24" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D24" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E24" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="F24" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G24" s="30">
         <v>11752</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H24" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J23" s="11" t="s">
+      <c r="I24" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="31" t="s">
         <v>58</v>
       </c>
     </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:H1" xr:uid="{E5E1C810-AA64-4EE6-A2D9-D85B15ADACA6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H8">
-      <sortCondition descending="1" ref="D1"/>
+  <autoFilter ref="C1:I1" xr:uid="{E5E1C810-AA64-4EE6-A2D9-D85B15ADACA6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:I8">
+      <sortCondition descending="1" ref="E1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E022C35-E719-437D-BD6A-E0E351A2541F}">
+  <dimension ref="B1:I38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="20.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1737</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="4">
+        <v>4449</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="4">
+        <v>11428</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B36" s="3"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="2:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B38" s="3"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>